--- a/models/6367_DCF_Model_20260906.xlsx
+++ b/models/6367_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020B0837-7C13-4C84-A00B-57035BAE0065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794FBE44-F525-4457-A405-E0C3A4159ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
     <t>vs Current Price</t>
   </si>
   <si>
-    <t>DCF - Perpetuity Growth</t>
+    <t>DCF - Perpetuity Growth [参考・Target不算入 — 追補6 §X]</t>
   </si>
   <si>
     <t>DCF - Exit Multiple</t>
@@ -92,7 +92,7 @@
     <t>Comps - PER Median [参考・Target不算入]</t>
   </si>
   <si>
-    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外）</t>
+    <t>Note: Target Mid は DCF 2法（PGM / Exit）の平均のみ。Comps 2法は [参考] で Target 不算入（EV&lt;ネットデットで株式価値が負になる手法は INVALID として平均から除外） ■【追補6 §X】PGMとExitの乖離が **3.31倍** で 3.0倍を超えたため、**乖離そのものを裁定トリガーとする追補6 §X により中点平均を禁止**し、どちらの脚を落とすかを判定した。■**観測倍率バンドテスト**: Peer の実測 EV/EBITDA の第1〜第3四分位バンドは **(6.837823670530699, 15.552094158010673, 5)倍**。これに対し **PGM逆算 4.32倍 / 仮定Exit 14.30倍**。**PGM法のみがバンドの外にあるため PGM法を[参考]に降格し、Target = Exit 単独**とした。■バンドテストは市場倍率を無条件のアンカーにするものではない（それではスクリーナーが市場の複写に堕する）。**実際に取引されているレンジの外に出た脚だけを取り除く**という位置づけである。</t>
   </si>
   <si>
     <t>DCF Valuation Range (PGM - Exit)</t>
@@ -1660,7 +1660,7 @@
     <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="45" t="s">
         <v>0</v>
       </c>
@@ -1668,19 +1668,19 @@
       <c r="D1" s="44"/>
       <c r="E1" s="44"/>
     </row>
-    <row r="3" spans="2:5" ht="18" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="43" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
     </row>
-    <row r="4" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1712,41 +1712,41 @@
         <v>20500</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5">
-        <f>IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0))</f>
-        <v>21290</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <f>IF(ISNUMBER(C17),ROUND(C17,0),"N/A")</f>
+        <v>30987</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="6" t="str">
         <f>IF(NOT(ISNUMBER(C12)),"N/A",IF(C12&gt;0.15,"BUY",IF(C12&gt;0.05,"HOLD","SELL")))</f>
-        <v>SELL</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>BUY</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="7">
         <f>IF(ISNUMBER(C10),(C10-C9)/C9,"N/A")</f>
-        <v>3.8536585365853658E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>0.51156097560975611</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>-0.43453658536585366</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>0.51156097560975611</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>0.70804878048780484</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0.27043902439024392</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="45" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
     </row>
-    <row r="21" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>11592 - 30987</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
@@ -1848,10 +1848,10 @@
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
         <f>"At "&amp;TEXT(C9,"#,##0")&amp;" the shares are valued below the large industrial peer median on EV/EBITDA; valuing the exit on that median supports "&amp;TEXT(C10,"#,##0")&amp;", or "&amp;TEXT(C12,"+0.0%;-0.0%")&amp;" from here."</f>
-        <v>At 20,500 the shares are valued below the large industrial peer median on EV/EBITDA; valuing the exit on that median supports 21,290, or +3.9% from here.</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>At 20,500 the shares are valued below the large industrial peer median on EV/EBITDA; valuing the exit on that median supports 30,987, or +51.2% from here.</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>24</v>
       </c>
@@ -1861,7 +1861,7 @@
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" t="str">
         <f>"The operating margin has fallen for four consecutive years while revenue grew, and nothing in the filings confirms the stabilisation the base case assumes behind "&amp;TEXT(C10,"#,##0")&amp;"."</f>
-        <v>The operating margin has fallen for four consecutive years while revenue grew, and nothing in the filings confirms the stabilisation the base case assumes behind 21,290.</v>
+        <v>The operating margin has fallen for four consecutive years while revenue grew, and nothing in the filings confirms the stabilisation the base case assumes behind 30,987.</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -1900,12 +1900,12 @@
     <col min="3" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
         <v>26</v>
       </c>
@@ -1919,12 +1919,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>31</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>5015036</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>32</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>3282519</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>1732517</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0.345464519098168</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>1317525</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>414992</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>275229</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>38</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>8.2749555536590372E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>39</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>5.4880762570797097E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>40</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>5.527830003566668E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>42</v>
       </c>
@@ -2133,12 +2133,12 @@
         <v>3.3169101922229501E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>44</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>465848</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>45</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>209081</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>46</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>256767</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>47</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>5.1199433064887272E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>48</v>
       </c>
@@ -2235,12 +2235,12 @@
         <v>4.169082734401109E-2</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>933484</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>51</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>829769</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>52</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>-103715</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>53</v>
       </c>
@@ -2319,12 +2319,12 @@
     <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>55</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>48</v>
       </c>
@@ -2342,7 +2342,7 @@
         <v>5.7700000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>56</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>57</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>2.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>58</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>0.88480000000000003</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>59</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>60</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>61</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>2.81E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>62</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>2.8199999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>63</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>64</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>65</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>278336120</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>66</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>161101</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>5015036</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>68</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>69</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>70</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>5015036</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>71</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>72</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>9.7211999999999993E-2</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>73</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>0.97257342929391166</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>74</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>2.742657070608831E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>75</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>9.5316494845360825E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>76</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>78</v>
       </c>
@@ -2530,7 +2530,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
         <v>79</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>40</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>84</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>0.65500000000000003</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>85</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>0.26019999999999999</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>31</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>6100852.9638976911</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>32</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>3996058.6913529877</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>33</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>2104794.2725447034</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>34</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>0.34500000000000003</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>86</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>1587441.9412061791</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>87</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>8.4800000000000028E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>88</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>517352.33133852435</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>89</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>129338.08283463109</v>
       </c>
     </row>
-    <row r="41" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>90</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>388014.24850389326</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>91</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>335546.91301437299</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>92</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>352019.21601689677</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>93</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>60209.308975399472</v>
       </c>
     </row>
-    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>94</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>311332.63652596995</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>95</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>0.63431044121737923</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>96</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>197481.54204015795</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
         <v>97</v>
       </c>
@@ -3007,7 +3007,7 @@
       <c r="F49" s="23"/>
       <c r="G49" s="23"/>
     </row>
-    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>98</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>1049686.2172359913</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>99</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>3685640.9005219229</v>
       </c>
     </row>
-    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>100</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>2337840.5057788799</v>
       </c>
     </row>
-    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>101</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>3387526.7230148711</v>
       </c>
     </row>
-    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>102</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>3226425.7230148711</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>103</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>11592</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
         <v>104</v>
       </c>
@@ -3071,7 +3071,7 @@
       <c r="F57" s="23"/>
       <c r="G57" s="23"/>
     </row>
-    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>98</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>1049686.2172359913</v>
       </c>
     </row>
-    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>105</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>852899.2443528974</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>106</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>12196459.194246434</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>100</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>7736341.412792217</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>101</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>8786027.6300282087</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>102</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>8624926.6300282087</v>
       </c>
     </row>
-    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>107</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>30987</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
         <v>108</v>
       </c>
@@ -3144,7 +3144,7 @@
       <c r="F66" s="23"/>
       <c r="G66" s="23"/>
     </row>
-    <row r="67" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
         <v>109</v>
       </c>
@@ -3161,12 +3161,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="68" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
         <v>77</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="70" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
         <v>114</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="71" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
         <v>115</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="72" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>116</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="73" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>117</v>
       </c>
@@ -3266,12 +3266,12 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>77</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>0.65500000000000003</v>
       </c>
     </row>
-    <row r="77" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
         <v>114</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="78" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>115</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>0.65500000000000003</v>
       </c>
     </row>
-    <row r="79" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
         <v>116</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>0.66200000000000003</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
         <v>117</v>
       </c>
@@ -3371,12 +3371,12 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>77</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>0.26019999999999999</v>
       </c>
     </row>
-    <row r="84" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
         <v>114</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>0.25729999999999997</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
         <v>115</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>0.26019999999999999</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
         <v>116</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>0.26600000000000001</v>
       </c>
     </row>
-    <row r="87" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
         <v>117</v>
       </c>
@@ -3500,17 +3500,17 @@
     <col min="3" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>120</v>
       </c>
@@ -3522,7 +3522,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>121</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>20500</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>65</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>278336120</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>122</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>5705890.46</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>66</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>161101</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>123</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>5866991.46</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>124</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>9.5316494845360825E-2</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>125</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>126</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>127</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>414992</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>128</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>414992</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>129</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>6100852.9638976911</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>130</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>3387526.7230148711</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>131</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>8.2749555536590372E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>132</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>2479464.7369851288</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>133</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>8908</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>134</v>
       </c>
@@ -3666,12 +3666,12 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>136</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>500551.146654866</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>137</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>667401.52887315466</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
         <v>138</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>1.6082274570911117</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
         <v>139</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>1.6082274570911117</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
         <v>140</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>0.10939479001093112</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
         <v>141</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>8065318.5935003804</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
         <v>142</v>
       </c>
@@ -3737,17 +3737,17 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
         <v>145</v>
       </c>
@@ -3775,12 +3775,12 @@
         <v>0.11531649484536083</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>148</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>0.86570538392736762</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>149</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>1.6171930873610232</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>150</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>2.2713554570607091</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>151</v>
       </c>
@@ -3892,12 +3892,12 @@
         <v>3.1006287036813376</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>148</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>8.468016790900581</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>149</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>7.5867255707695698</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>150</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>6.8282137405002103</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>151</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>5.8794970095910601</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
         <v>153</v>
       </c>
@@ -4021,7 +4021,7 @@
       <c r="H47" s="23"/>
       <c r="I47" s="23"/>
     </row>
-    <row r="48" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>148</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>881362.73883314722</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>149</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>942637.639859227</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>150</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>1007593.0832914223</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>151</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>1111645.9728340725</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
         <v>154</v>
       </c>
@@ -4145,7 +4145,7 @@
       <c r="H52" s="23"/>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>148</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>2.1238065765921927</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>149</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>2.2714597868374016</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>150</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>2.4279819449324864</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>151</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>2.6787166326918892</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
         <v>155</v>
       </c>
@@ -4269,12 +4269,12 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>157</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>736984.62864251784</v>
       </c>
     </row>
-    <row r="62" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
         <v>158</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="31">
         <v>4.1399999999999999E-2</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>3.5496377450374608</v>
       </c>
     </row>
-    <row r="64" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="31">
         <v>6.2100000000000002E-2</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>2.3664251633583069</v>
       </c>
     </row>
-    <row r="65" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
         <v>161</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>1.7759008092746795</v>
       </c>
     </row>
-    <row r="66" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="31">
         <v>0.10340000000000001</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>1.4212282654211883</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="31">
         <v>0.1241</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>1.1841660164750272</v>
       </c>
     </row>
-    <row r="69" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
         <v>162</v>
       </c>
@@ -4371,7 +4371,7 @@
       <c r="H69" s="9"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
         <v>163</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>8.4881487793656802</v>
       </c>
     </row>
-    <row r="71" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
         <v>164</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>1.1698802281778236</v>
       </c>
     </row>
-    <row r="72" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
         <v>165</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>5.8497438302595564</v>
       </c>
     </row>
-    <row r="73" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
         <v>166</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>5.4702274312011658</v>
       </c>
     </row>
-    <row r="74" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
         <v>167</v>
       </c>
@@ -4416,12 +4416,12 @@
         <v>14.333259113904496</v>
       </c>
     </row>
-    <row r="75" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="77" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
         <v>169</v>
       </c>
@@ -4433,13 +4433,13 @@
       <c r="H77" s="23"/>
       <c r="I77" s="23"/>
     </row>
-    <row r="78" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="str">
         <f>"At "&amp;TEXT(C6,"#,##0")&amp;" yen the market is paying for a steady-state operating profit of "&amp;TEXT(F49,"#,##0")&amp;" mn JPY - "&amp;TEXT(F54,"0.00")&amp;"x the FY2026 cycle peak of "&amp;TEXT(C15,"#,##0")&amp;" mn - reached in 5 years and sustained for ever, against "&amp;TEXT(C14,"#,##0")&amp;" mn actually earned in FY2026."</f>
         <v>At 20,500 yen the market is paying for a steady-state operating profit of 736,985 mn JPY - 1.78x the FY2026 cycle peak of 414,992 mn - reached in 5 years and sustained for ever, against 414,992 mn actually earned in FY2026.</v>
       </c>
     </row>
-    <row r="79" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="str">
         <f>"Even with no ramp at all (Block A) the price needs "&amp;TEXT(C25,"#,##0")&amp;" mn, or "&amp;TEXT(C26,"0.00")&amp;"x the peak. The base case supports an EV of only "&amp;TEXT(C17,"#,##0")&amp;" mn, leaving "&amp;TEXT(C20,"#,##0")&amp;" yen per share of the current price unexplained by mid-cycle economics."</f>
         <v>Even with no ramp at all (Block A) the price needs 667,402 mn, or 1.61x the peak. The base case supports an EV of only 3,387,527 mn, leaving 8,908 yen per share of the current price unexplained by mid-cycle economics.</v>
@@ -4464,12 +4464,12 @@
     <col min="3" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>171</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
         <v>173</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>174</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>175</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>176</v>
       </c>
@@ -4590,7 +4590,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
     </row>
-    <row r="9" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>31</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>6100852.9638976911</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>32</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>3996058.6913529877</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
         <v>177</v>
       </c>
@@ -4657,7 +4657,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
     </row>
-    <row r="12" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>178</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>1136597.264506967</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>179</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>1423253.7804818861</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>180</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>2559851.0449888529</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="33" t="s">
         <v>181</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>492664.77016680676</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>182</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>492664.77016680676</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
         <v>183</v>
       </c>
@@ -4810,7 +4810,7 @@
       <c r="G17" s="23"/>
       <c r="H17" s="23"/>
     </row>
-    <row r="18" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
         <v>184</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>2067186.274822046</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
         <v>93</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>60209.308975399472</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
         <v>185</v>
       </c>
@@ -4878,7 +4878,7 @@
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
         <v>79</v>
       </c>
@@ -4895,12 +4895,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>77</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>114</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>115</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>116</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>117</v>
       </c>
@@ -5000,12 +5000,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>77</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>114</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>115</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>116</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>117</v>
       </c>
@@ -5105,12 +5105,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>77</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>114</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>115</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>116</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>117</v>
       </c>
@@ -5231,17 +5231,17 @@
     <col min="17" max="17" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="28" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>205</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>3254652</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>207</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>6568369</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>209</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>4484266</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>211</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>5492689</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>213</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>3088566</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>215</v>
       </c>
@@ -5611,12 +5611,12 @@
         <v>3661793</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>8.0790119375045627E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>219</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>8.937261063091223E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>220</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>9.0930823461409294E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>221</v>
       </c>
@@ -5715,12 +5715,12 @@
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
     </row>
-    <row r="20" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>223</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>691198</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>224</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>275229</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>225</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>278336120</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>66</v>
       </c>
@@ -5752,12 +5752,12 @@
         <v>161101</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>227</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>35015</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>228</v>
       </c>
@@ -5794,12 +5794,12 @@
     <col min="3" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>230</v>
       </c>
@@ -5822,12 +5822,12 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="s">
         <v>234</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="39">
         <f>$C$3-0.015</f>
         <v>8.0316494845360825E-2</v>
@@ -5894,7 +5894,7 @@
         <v>15661</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="39">
         <f>$C$3-0.01</f>
         <v>8.531649484536083E-2</v>
@@ -5928,7 +5928,7 @@
         <v>14440</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39">
         <f>$C$3-0.005</f>
         <v>9.031649484536082E-2</v>
@@ -5962,7 +5962,7 @@
         <v>13387</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="39">
         <f>$C$3</f>
         <v>9.5316494845360825E-2</v>
@@ -5996,7 +5996,7 @@
         <v>12470</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="39">
         <f>$C$3+0.005</f>
         <v>0.10031649484536083</v>
@@ -6030,7 +6030,7 @@
         <v>11664</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="39">
         <f>$C$3+0.01</f>
         <v>0.10531649484536082</v>
@@ -6064,7 +6064,7 @@
         <v>10950</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="39">
         <f>$C$3+0.015</f>
         <v>0.11031649484536082</v>
@@ -6098,12 +6098,12 @@
         <v>10313</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="40" t="s">
         <v>236</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="39">
         <f>$C$3-0.015</f>
         <v>8.0316494845360825E-2</v>
@@ -6170,7 +6170,7 @@
         <v>39375</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="39">
         <f>$C$3-0.01</f>
         <v>8.531649484536083E-2</v>
@@ -6204,7 +6204,7 @@
         <v>38499</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="39">
         <f>$C$3-0.005</f>
         <v>9.031649484536082E-2</v>
@@ -6238,7 +6238,7 @@
         <v>37648</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="39">
         <f>$C$3</f>
         <v>9.5316494845360825E-2</v>
@@ -6272,7 +6272,7 @@
         <v>36819</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="39">
         <f>$C$3+0.005</f>
         <v>0.10031649484536083</v>
@@ -6306,7 +6306,7 @@
         <v>36012</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="39">
         <f>$C$3+0.01</f>
         <v>0.10531649484536082</v>
@@ -6340,7 +6340,7 @@
         <v>35226</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="39">
         <f>$C$3+0.015</f>
         <v>0.11031649484536082</v>
@@ -6374,7 +6374,7 @@
         <v>34461</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
         <v>237</v>
       </c>
@@ -6411,12 +6411,12 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="18" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
         <v>239</v>
       </c>
@@ -6496,12 +6496,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>261</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>263</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>265</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>267</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>269</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>270</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
         <v>272</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>274</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>276</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>278</v>
       </c>
@@ -6581,7 +6581,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>280</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>281</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>282</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>284</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>285</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>286</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>288</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>290</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>292</v>
       </c>
@@ -6653,7 +6653,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>293</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>294</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>295</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>297</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>299</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>301</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>303</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>305</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>307</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>309</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>311</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>313</v>
       </c>
@@ -6749,7 +6749,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>315</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>316</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>318</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>320</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>322</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>324</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>326</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>328</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="52" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>330</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="53" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>332</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="54" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
         <v>334</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="55" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
         <v>336</v>
       </c>
@@ -6845,7 +6845,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="56" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
         <v>338</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="57" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
         <v>340</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="58" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
         <v>342</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="59" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
         <v>344</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="60" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
         <v>346</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="61" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
         <v>348</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="62" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
         <v>350</v>
       </c>
@@ -6901,7 +6901,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="63" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
         <v>352</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="64" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>354</v>
       </c>
